--- a/src/assets/produit.xlsx
+++ b/src/assets/produit.xlsx
@@ -32,8 +32,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="6">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="58" formatCode="m/d/yy"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -397,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,24 +426,492 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>.</v>
+        <v>SIMATIC, Standard mounting rail 35mm, Length 483 mm for 19" cabinet ref:6ES5710-8MA11</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>6ES5710-8MA11</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>https://www.eibabo.com/media/image/1f/59/a4/EB15507589KAGcUuPta2yUw_600x600.jpg</v>
+      </c>
+      <c r="D2">
+        <v>210</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-09-07</v>
+        <v>+046181-12</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DIGITAL INPUT SM 1221, 16DI, 24V DC ref: 6ES7221-1BH32-0XB0</v>
+      </c>
+      <c r="B3" t="str">
+        <v>6ES7221-1BH32-0XB0</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://mall.industry.siemens.com/mall/collaterals/files/204/jpg/06/10/G_ST70_XX_00884i.jpg</v>
+      </c>
+      <c r="D3">
+        <v>430</v>
+      </c>
+      <c r="E3" t="str">
+        <v>+046181-12</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SIMATIC S7-1200, Digital output SM 1222, 16 DO, 24 V DC, transistor 0.5 A RÈf:6ES7222-1BH32-0XB0</v>
+      </c>
+      <c r="B4" t="str">
+        <v>6ES7222-1BH32-0XB0</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://sieportal.siemens.com/en-za/products-services/detail/6ES7222-1BH32-0XB0?tree=CatalogTree</v>
+      </c>
+      <c r="D4">
+        <v>450</v>
+      </c>
+      <c r="E4" t="str">
+        <v>+046181-12</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SIMATIC S7-1200, Analog input, SM 1231, 8 AI, bit+sign or (13 bit ADC)</v>
+      </c>
+      <c r="B5" t="str">
+        <v>6ES7231-4HF32-0XB0</v>
+      </c>
+      <c r="C5" t="str">
+        <v>https://sieportal.siemens.com/en-us/products-services/detail/6ES7231-4HF32-0XB0?tree=CatalogTree</v>
+      </c>
+      <c r="D5">
+        <v>1050</v>
+      </c>
+      <c r="E5" t="str">
+        <v>+046181-12</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SIMATIC S7-1200, ANALOG OUTPUT, SM 1232, 4 AO,MA, 13 BIT RESOLUTION</v>
+      </c>
+      <c r="B6" t="str">
+        <v>6ES7232-4HD32-0XB0</v>
+      </c>
+      <c r="C6" t="str">
+        <v>https://sieportal.siemens.com/en-fi/products-services/detail/6ES7232-4HD32-0XB0?tree=CatalogTree</v>
+      </c>
+      <c r="D6">
+        <v>1100</v>
+      </c>
+      <c r="E6" t="str">
+        <v>+046181-12</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SITOP PSU100S 24 V/10 A Stabilized power supply input: 120/230 V AC, output: DC 24 V/10 A</v>
+      </c>
+      <c r="B7" t="str">
+        <v>6EP1334-2BA20</v>
+      </c>
+      <c r="C7" t="str">
+        <v>https://sieportal.siemens.com/en-sa/products-services/detail/6EP1334-2BA20?tree=CatalogTree</v>
+      </c>
+      <c r="D7">
+        <v>722.5</v>
+      </c>
+      <c r="E7" t="str">
+        <v>+046181-12</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Industrial Ethernet FC TP Standard cable, GP 2x2 (PROFINET Type A), TP installation cable for connection to IE FC RJ45 2x2, for universal use,4-core, shielded CAT 5E, sold by the meter, delivery length max. 4000 m minimum order 20 m</v>
+      </c>
+      <c r="B8" t="str">
+        <v>6XV1840-2AH10</v>
+      </c>
+      <c r="C8" t="str">
+        <v>https://sieportal.siemens.com/en-bg/products-services/detail/6XV1840-2AH10?tree=CatalogTree</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8" t="str">
+        <v>+046181-12</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>6ES7214-1AG40-0XB0, CPU COMPACT, DC/DC/DC E/S EMBARQUEES: 14 ETOR 24V CC;10 STOR 24 V CC; 2 EA 0 - 10V CC, ALIMENTATION: CC 20,4 - 28,8 V CC, MEMOIRE PROGR./DONNEES 75 KO</v>
+      </c>
+      <c r="B9" t="str">
+        <v>6ES7214-1AG40-0XB0</v>
+      </c>
+      <c r="C9" t="str">
+        <v>https://sieportal.siemens.com/en-us/products-services/detail/6ES7214-1AG40-0XB0?tree=CatalogTree</v>
+      </c>
+      <c r="D9">
+        <v>1300</v>
+      </c>
+      <c r="E9" t="str">
+        <v>+046181-12</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SIMATIC DP, mounting rail for ET 200M, 620 mm long, for holding bus modules for removal and insertion function</v>
+      </c>
+      <c r="B10" t="str">
+        <v>6ES7195-1GG30-0XA0</v>
+      </c>
+      <c r="C10" t="str">
+        <v>https://sieportal.siemens.com/en-bg/products-services/detail/6ES7195-1GG30-0XA0?tree=CatalogTree</v>
+      </c>
+      <c r="D10">
+        <v>290</v>
+      </c>
+      <c r="E10" t="str">
+        <v>+046215-12</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SIMATIC S7-300, CPU 315-2DP CPU WITH MPI INTERFACE INTEGRATED 24 V DC POWER SUPPLY 256 KBYTE WORKING MEMORY 2. INTERFACE DP-MASTER/SLAVE MICRO MEMORY CARD NECESSARY</v>
+      </c>
+      <c r="B11" t="str">
+        <v>6ES7315-2AH14-0AB0</v>
+      </c>
+      <c r="C11" t="str">
+        <v>https://www.industry-mobile-support.siemens-info.com/en/product/6ES73152AH140AB0</v>
+      </c>
+      <c r="D11">
+        <v>3700</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SIMATIC DP, Couplage ET 200M IM 153-2 High Feature pour max. 12 modules S7-300 apte ‡ la redondance, horodatage convient pour le mode isochrone nouvelles fonctionnalitÈs: jusqu'‡ 12 modules utilisables Initiative esclave pour pilote ES et commutateur ES capacitÈs fonctionnelles Ètendues pour variables secondaires HART exploitation des modules ‡ 64 canaux 32 signaux/emplacement +++Tenir compte de la note de compatibilitÈ dans le manuel</v>
+      </c>
+      <c r="B12" t="str">
+        <v>6ES7153-2BA10-0XB0</v>
+      </c>
+      <c r="C12" t="str">
+        <v>https://fr.wiautomation.com/siemens/modules/simatic-s7/s7-300/6ES71532BA100XB0</v>
+      </c>
+      <c r="D12">
+        <v>1105.3</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>6 96,120 SIMATIC S7-300, RAIL L=480MM</v>
+      </c>
+      <c r="B13" t="str">
+        <v>6ES7390-1AE80-0AA0</v>
+      </c>
+      <c r="C13" t="str">
+        <v>https://mall.industry.siemens.com/mall/en/fescomelsaownuy/Catalog/Product?mlfb=6ES7390-1AE80-0AA0&amp;SiepCountryCode=OE</v>
+      </c>
+      <c r="D13">
+        <v>96.12</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SIMATIC DP, module de bus pour ET 200M pour le montage de deux modules pÈriphÈriques 40mm de large pour fonction DÈbrochage et embrochage</v>
+      </c>
+      <c r="B14" t="str">
+        <v>6ES7195-7HB00-0XA0</v>
+      </c>
+      <c r="C14" t="str">
+        <v>https://mall.industry.siemens.com/mall/en/inosatavtomatica/Catalog/Product?mlfb=6ES7195-7HB00-0XA0&amp;SiepCountryCode=OE</v>
+      </c>
+      <c r="D14">
+        <v>307.584</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SIMATIC DP, module de bus pour ET 200M pour le montage de 2 IM153-2 Red. pour fonction DÈbrochage et embrochage pendant le fonctionnement (Run)</v>
+      </c>
+      <c r="B15" t="str">
+        <v>6ES7195-7HD10-0XA0</v>
+      </c>
+      <c r="C15" t="str">
+        <v>https://sieportal.siemens.com/en-au/products-services/detail/6ES7195-7HD10-0XA0?tree=CatalogTree</v>
+      </c>
+      <c r="D15">
+        <v>365.256</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SIMATIC S7-300 stabilized power supply PS307 input: 120/230 V AC output: 24 V DC/10 A</v>
+      </c>
+      <c r="B16" t="str">
+        <v>6ES7307-1KA02-0AA0</v>
+      </c>
+      <c r="C16" t="str">
+        <v>https://sieportal.siemens.com/en-gb/products-services/detail/6es7307-1ka02-0aa0?tree=CatalogTree</v>
+      </c>
+      <c r="D16">
+        <v>557.496</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SIMATIC S7-300, ANALOG INPUT SM 331, FLOATING,8AI, RESOLUTION 9/12/14 BITS,U/I/THERMOCOUPLE/RESISTANCE ALERT,DIAGNOSTICS; 1X20PIN REMOVE/INSERT W.</v>
+      </c>
+      <c r="B17" t="str">
+        <v>6ES7331-7KF02-0AB0</v>
+      </c>
+      <c r="C17" t="str">
+        <v>https://sieportal.siemens.com/en-ww/products-services/detail/6ES7331-7KF02-0AB0?tree=CatalogTree</v>
+      </c>
+      <c r="D17">
+        <v>1153.4</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SIMATIC S7-300, ANALOG OUTPUT SM 332,OPTICALLY ISOLATED, 4 AO, U/I; DIAGNOSTICS;RESOLUTION 11/12 BITS, 20 PIN, REMOVE/INSERT W. ACTIVE, BACKPLANE BUS</v>
+      </c>
+      <c r="B18" t="str">
+        <v>6ES7332-5HD01-0AB0</v>
+      </c>
+      <c r="C18" t="str">
+        <v>https://www.industry-mobile-support.siemens-info.com/en/product/6ES73325HD010AB0</v>
+      </c>
+      <c r="D18">
+        <v>865.08</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SIMATIC DP,BUS CONNECTOR FOR PROFIBUS UP TO 12 MBIT/S 90 DEGREE ANGLE CABLE OUTLET, IPCD TECHOLOGY FAST CONNECT, WITHOUT PG SOCKET 15,8 X 59 X 35,6 MM (WXHXD)</v>
+      </c>
+      <c r="B19" t="str">
+        <v>6ES7972-0BA52-0XA0</v>
+      </c>
+      <c r="C19" t="str">
+        <v>https://sieportal.siemens.com/en-ww/products-services/detail/6ES7972-0BA52-0XA0?tree=CatalogTree</v>
+      </c>
+      <c r="D19">
+        <v>96.12</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>PROFIBUS FC Standard Cable GP, bus cable 2-wire, shielded special configuration for quick assembly,Delivery unit: max. 1000 m, Minimum order 20 m Sold by the meter</v>
+      </c>
+      <c r="B20" t="str">
+        <v>6XV1830-0EH10</v>
+      </c>
+      <c r="C20" t="str">
+        <v>https://sieportal.siemens.com/en-dz/products-services/detail/6XV1830-0EH10?tree=CatalogTree</v>
+      </c>
+      <c r="D20">
+        <v>6.247</v>
+      </c>
+      <c r="E20" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SIMATIC S7-300, Front connector for signal modules with spring-loaded contacts, 20-pole</v>
+      </c>
+      <c r="B21" t="str">
+        <v>6ES7392-1BJ00-0AA0</v>
+      </c>
+      <c r="C21" t="str">
+        <v>https://www.industry-mobile-support.siemens-info.com/en/product/6ES73921BJ000AA0</v>
+      </c>
+      <c r="D21">
+        <v>96.12</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SCALANCE XB008 unmanaged Industrial Ethernet</v>
+      </c>
+      <c r="B22" t="str">
+        <v>6GK5008-0BA00-1AB2</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>and line topologies; LED diagnostics, IP20, 24 V DC</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>power supply, with 8x 10/100 Mbit/s twisted pair</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>ports with RJ45 sockets; manual available as a</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>download .RÈf: 6GK5008-0BA00-1AB2</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v>2026-09-08</v>
+      </c>
+      <c r="F26" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F26"/>
   </ignoredErrors>
 </worksheet>
 </file>